--- a/Bayesian/BayesFactor_Results_Adults_TYPE.xlsx
+++ b/Bayesian/BayesFactor_Results_Adults_TYPE.xlsx
@@ -1,98 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10412"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anthi2revithiadou/Desktop/Lg&amp;Sp_reviews/article/revision/Supplemental_materials/Bayesian/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B4761AE-7F9F-904C-8B1E-B41C7D9E06C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="660" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
-  <si>
-    <t>Class</t>
-  </si>
-  <si>
-    <t>Property</t>
-  </si>
-  <si>
-    <t>Lexical_p0_type</t>
-  </si>
-  <si>
-    <t>Raw_successes</t>
-  </si>
-  <si>
-    <t>raw_total</t>
-  </si>
-  <si>
-    <t>observed_proportion</t>
-  </si>
-  <si>
-    <t>posterior_mean_p</t>
-  </si>
-  <si>
-    <t>posterior_median_p</t>
-  </si>
-  <si>
-    <t>ci_95_p_lower</t>
-  </si>
-  <si>
-    <t>ci_95_p_upper</t>
-  </si>
-  <si>
-    <t>BF01</t>
-  </si>
-  <si>
-    <t>BF10</t>
-  </si>
-  <si>
-    <t>aF</t>
-  </si>
-  <si>
-    <t>APU</t>
-  </si>
-  <si>
-    <t>PU</t>
-  </si>
-  <si>
-    <t>iF</t>
-  </si>
-  <si>
-    <t>iN</t>
-  </si>
-  <si>
-    <t>isM</t>
-  </si>
-  <si>
-    <t>maN</t>
-  </si>
-  <si>
-    <t>Inf</t>
-  </si>
-  <si>
-    <t>oN</t>
-  </si>
-  <si>
-    <t>osM</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -192,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -226,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -261,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -437,60 +350,85 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="12" max="12" width="25.33203125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Lexical_p0_type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Raw_successes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>raw_total</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>observed_proportion</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>posterior_mean_p</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>posterior_median_p</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ci_95_p_lower</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ci_95_p_upper</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>BF01</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>BF10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aF</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>APU</t>
+        </is>
       </c>
       <c r="C2">
-        <v>0.22589999999999999</v>
+        <v>0.2259</v>
       </c>
       <c r="D2">
         <v>255</v>
@@ -499,36 +437,40 @@
         <v>945</v>
       </c>
       <c r="F2">
-        <v>0.26984126984126983</v>
+        <v>0.2698412698412698</v>
       </c>
       <c r="G2">
         <v>0.2689531634821945</v>
       </c>
       <c r="H2">
-        <v>0.26876226607005749</v>
+        <v>0.2687622660700575</v>
       </c>
       <c r="I2">
-        <v>0.24157248891943811</v>
+        <v>0.2415724889194381</v>
       </c>
       <c r="J2">
-        <v>0.29742967727517478</v>
+        <v>0.2974296772751748</v>
       </c>
       <c r="K2">
-        <v>4.6329446386589819E-2</v>
+        <v>0.04632944638658982</v>
       </c>
       <c r="L2">
-        <v>21.584544560615619</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
+        <v>21.58454456061562</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aF</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PU</t>
+        </is>
       </c>
       <c r="C3">
-        <v>0.58099999999999996</v>
+        <v>0.581</v>
       </c>
       <c r="D3">
         <v>672</v>
@@ -537,36 +479,40 @@
         <v>945</v>
       </c>
       <c r="F3">
-        <v>0.71111111111111114</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="G3">
-        <v>0.70881766740603858</v>
+        <v>0.7088176674060386</v>
       </c>
       <c r="H3">
-        <v>0.70888713235797662</v>
+        <v>0.7088871323579766</v>
       </c>
       <c r="I3">
-        <v>0.67971120912143268</v>
+        <v>0.6797112091214327</v>
       </c>
       <c r="J3">
-        <v>0.73715350033678972</v>
+        <v>0.7371535003367897</v>
       </c>
       <c r="K3">
-        <v>1.3083786122883719E-13</v>
+        <v>1.308378612288372E-13</v>
       </c>
       <c r="L3">
-        <v>7643047590414.1113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
+        <v>7643047590414.111</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>iF</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>APU</t>
+        </is>
       </c>
       <c r="C4">
-        <v>0.60170000000000001</v>
+        <v>0.6017</v>
       </c>
       <c r="D4">
         <v>133</v>
@@ -575,36 +521,40 @@
         <v>945</v>
       </c>
       <c r="F4">
-        <v>0.14074074074074069</v>
+        <v>0.1407407407407407</v>
       </c>
       <c r="G4">
-        <v>0.14981780709458489</v>
+        <v>0.1498178070945849</v>
       </c>
       <c r="H4">
-        <v>0.14956728072739839</v>
+        <v>0.1495672807273984</v>
       </c>
       <c r="I4">
-        <v>0.12796028272919049</v>
+        <v>0.1279602827291905</v>
       </c>
       <c r="J4">
-        <v>0.17260943504724011</v>
+        <v>0.1726094350472401</v>
       </c>
       <c r="K4">
-        <v>3.7497967535679012E-126</v>
+        <v>3.749796753567901E-126</v>
       </c>
       <c r="L4">
-        <v>2.6668112052966819E+125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
+        <v>2.666811205296682E+125</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>iF</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PU</t>
+        </is>
       </c>
       <c r="C5">
-        <v>0.15759999999999999</v>
+        <v>0.1576</v>
       </c>
       <c r="D5">
         <v>719</v>
@@ -613,36 +563,40 @@
         <v>945</v>
       </c>
       <c r="F5">
-        <v>0.76084656084656088</v>
+        <v>0.7608465608465609</v>
       </c>
       <c r="G5">
-        <v>0.74919613179283395</v>
+        <v>0.749196131792834</v>
       </c>
       <c r="H5">
-        <v>0.74936578030188306</v>
+        <v>0.7493657803018831</v>
       </c>
       <c r="I5">
-        <v>0.72093113373549289</v>
+        <v>0.7209311337354929</v>
       </c>
       <c r="J5">
-        <v>0.77628475746696746</v>
+        <v>0.7762847574669675</v>
       </c>
       <c r="K5">
         <v>4.663776621369343E-295</v>
       </c>
       <c r="L5">
-        <v>2.1441850268257221E+294</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
+        <v>2.144185026825722E+294</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>iN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>APU</t>
+        </is>
       </c>
       <c r="C6">
-        <v>9.7000000000000003E-3</v>
+        <v>0.0097</v>
       </c>
       <c r="D6">
         <v>80</v>
@@ -651,36 +605,40 @@
         <v>945</v>
       </c>
       <c r="F6">
-        <v>8.4656084656084651E-2</v>
+        <v>0.08465608465608465</v>
       </c>
       <c r="G6">
-        <v>7.5839191829926877E-2</v>
+        <v>0.07583919182992688</v>
       </c>
       <c r="H6">
-        <v>7.5566078766050676E-2</v>
+        <v>0.07556607876605068</v>
       </c>
       <c r="I6">
-        <v>6.0233934910142617E-2</v>
+        <v>0.06023393491014262</v>
       </c>
       <c r="J6">
-        <v>9.2790020015506416E-2</v>
+        <v>0.09279002001550642</v>
       </c>
       <c r="K6">
-        <v>8.3968083919908068E-69</v>
+        <v>8.396808391990807E-69</v>
       </c>
       <c r="L6">
-        <v>1.1909286878021871E+68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
+        <v>1.190928687802187E+68</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>iN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PU</t>
+        </is>
       </c>
       <c r="C7">
-        <v>0.95420000000000005</v>
+        <v>0.9542</v>
       </c>
       <c r="D7">
         <v>813</v>
@@ -689,36 +647,40 @@
         <v>945</v>
       </c>
       <c r="F7">
-        <v>0.86031746031746037</v>
+        <v>0.8603174603174604</v>
       </c>
       <c r="G7">
-        <v>0.86542758212729398</v>
+        <v>0.865427582127294</v>
       </c>
       <c r="H7">
-        <v>0.86569088415920326</v>
+        <v>0.8656908841592033</v>
       </c>
       <c r="I7">
-        <v>0.84342666307369163</v>
+        <v>0.8434266630736916</v>
       </c>
       <c r="J7">
-        <v>0.88566408322508572</v>
+        <v>0.8856640832250857</v>
       </c>
       <c r="K7">
-        <v>6.0241775634721147E-34</v>
+        <v>6.024177563472115E-34</v>
       </c>
       <c r="L7">
-        <v>1.6599776309110601E+33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
+        <v>1.65997763091106E+33</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>isM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>APU</t>
+        </is>
       </c>
       <c r="C8">
-        <v>1.4999999999999999E-2</v>
+        <v>0.012</v>
       </c>
       <c r="D8">
         <v>43</v>
@@ -727,36 +689,40 @@
         <v>945</v>
       </c>
       <c r="F8">
-        <v>4.5502645502645503E-2</v>
+        <v>0.0455026455026455</v>
       </c>
       <c r="G8">
-        <v>4.1176041327443923E-2</v>
+        <v>0.04028018298840635</v>
       </c>
       <c r="H8">
-        <v>4.088087960946768E-2</v>
+        <v>0.0399423043563591</v>
       </c>
       <c r="I8">
-        <v>3.0165632060633021E-2</v>
+        <v>0.02923198663124568</v>
       </c>
       <c r="J8">
-        <v>5.3970948944030379E-2</v>
+        <v>0.05300154648969986</v>
       </c>
       <c r="K8">
-        <v>9.1785376143686948E-10</v>
+        <v>2.294729210738153E-13</v>
       </c>
       <c r="L8">
-        <v>1089498177.1764309</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
+        <v>4357812657460.907</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>isM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PU</t>
+        </is>
       </c>
       <c r="C9">
-        <v>0.54149999999999998</v>
+        <v>0.5415</v>
       </c>
       <c r="D9">
         <v>713</v>
@@ -765,36 +731,40 @@
         <v>945</v>
       </c>
       <c r="F9">
-        <v>0.75449735449735444</v>
+        <v>0.7544973544973544</v>
       </c>
       <c r="G9">
-        <v>0.75080846053144235</v>
+        <v>0.7508084605314423</v>
       </c>
       <c r="H9">
-        <v>0.75098247553370834</v>
+        <v>0.7509824755337083</v>
       </c>
       <c r="I9">
         <v>0.7228423038502545</v>
       </c>
       <c r="J9">
-        <v>0.77768039794662869</v>
+        <v>0.7776803979466287</v>
       </c>
       <c r="K9">
         <v>2.310650572110718E-34</v>
       </c>
       <c r="L9">
-        <v>4.3277854820191463E+33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
+        <v>4.327785482019146E+33</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>maN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>APU</t>
+        </is>
       </c>
       <c r="C10">
-        <v>0.99999000000000005</v>
+        <v>0.99999</v>
       </c>
       <c r="D10">
         <v>849</v>
@@ -803,36 +773,42 @@
         <v>945</v>
       </c>
       <c r="F10">
-        <v>0.89841269841269844</v>
+        <v>0.8984126984126984</v>
       </c>
       <c r="G10">
-        <v>0.93592452235253698</v>
+        <v>0.935924522352537</v>
       </c>
       <c r="H10">
-        <v>0.93618314207252762</v>
+        <v>0.9361831420725276</v>
       </c>
       <c r="I10">
         <v>0.9198501311136319</v>
       </c>
       <c r="J10">
-        <v>0.94984613178712007</v>
+        <v>0.9498461317871201</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
-      <c r="L10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>14</v>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>maN</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PU</t>
+        </is>
       </c>
       <c r="C11">
-        <v>1.0000000000000001E-5</v>
+        <v>1E-05</v>
       </c>
       <c r="D11">
         <v>90</v>
@@ -841,36 +817,42 @@
         <v>945</v>
       </c>
       <c r="F11">
-        <v>9.5238095238095233E-2</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="G11">
-        <v>5.8271690931921062E-2</v>
+        <v>0.05827169093192106</v>
       </c>
       <c r="H11">
-        <v>5.7913305014433203E-2</v>
+        <v>0.0579133050144332</v>
       </c>
       <c r="I11">
-        <v>4.4772866258004293E-2</v>
+        <v>0.04477286625800429</v>
       </c>
       <c r="J11">
-        <v>7.349373908542986E-2</v>
+        <v>0.07349373908542986</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
-      <c r="L11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>oN</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>APU</t>
+        </is>
       </c>
       <c r="C12">
-        <v>0.62560000000000004</v>
+        <v>0.6256</v>
       </c>
       <c r="D12">
         <v>569</v>
@@ -879,36 +861,40 @@
         <v>945</v>
       </c>
       <c r="F12">
-        <v>0.60211640211640216</v>
+        <v>0.6021164021164022</v>
       </c>
       <c r="G12">
-        <v>0.60268304841471521</v>
+        <v>0.6026830484147152</v>
       </c>
       <c r="H12">
-        <v>0.60281332683500743</v>
+        <v>0.6028133268350074</v>
       </c>
       <c r="I12">
         <v>0.5714170288327598</v>
       </c>
       <c r="J12">
-        <v>0.63315137763926543</v>
+        <v>0.6331513776392654</v>
       </c>
       <c r="K12">
         <v>2.623323478958882</v>
       </c>
       <c r="L12">
-        <v>0.38119584108509158</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>14</v>
+        <v>0.3811958410850916</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>oN</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PU</t>
+        </is>
       </c>
       <c r="C13">
-        <v>0.26500000000000001</v>
+        <v>0.265</v>
       </c>
       <c r="D13">
         <v>318</v>
@@ -917,36 +903,40 @@
         <v>945</v>
       </c>
       <c r="F13">
-        <v>0.33650793650793648</v>
+        <v>0.3365079365079365</v>
       </c>
       <c r="G13">
-        <v>0.33514746761070269</v>
+        <v>0.3351474676107027</v>
       </c>
       <c r="H13">
-        <v>0.33501484515740709</v>
+        <v>0.3350148451574071</v>
       </c>
       <c r="I13">
-        <v>0.30577879064333519</v>
+        <v>0.3057787906433352</v>
       </c>
       <c r="J13">
-        <v>0.36492152670964628</v>
+        <v>0.3649215267096463</v>
       </c>
       <c r="K13">
-        <v>3.5793681731883552E-5</v>
+        <v>3.579368173188355E-05</v>
       </c>
       <c r="L13">
         <v>27937.89159468445</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>13</v>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>osM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>APU</t>
+        </is>
       </c>
       <c r="C14">
-        <v>0.35649999999999998</v>
+        <v>0.3565</v>
       </c>
       <c r="D14">
         <v>457</v>
@@ -955,36 +945,40 @@
         <v>945</v>
       </c>
       <c r="F14">
-        <v>0.48359788359788358</v>
+        <v>0.4835978835978836</v>
       </c>
       <c r="G14">
-        <v>0.48127442170849721</v>
+        <v>0.4812744217084972</v>
       </c>
       <c r="H14">
-        <v>0.48125031148858932</v>
+        <v>0.4812503114885893</v>
       </c>
       <c r="I14">
-        <v>0.44925973530362129</v>
+        <v>0.4492597353036213</v>
       </c>
       <c r="J14">
-        <v>0.51248626037245149</v>
+        <v>0.5124862603724515</v>
       </c>
       <c r="K14">
-        <v>1.7299499530844511E-13</v>
+        <v>1.729949953084451E-13</v>
       </c>
       <c r="L14">
         <v>5780514044449.832</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" t="s">
-        <v>14</v>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>osM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PU</t>
+        </is>
       </c>
       <c r="C15">
-        <v>0.16819999999999999</v>
+        <v>0.1682</v>
       </c>
       <c r="D15">
         <v>345</v>
@@ -993,22 +987,22 @@
         <v>945</v>
       </c>
       <c r="F15">
-        <v>0.36507936507936511</v>
+        <v>0.3650793650793651</v>
       </c>
       <c r="G15">
-        <v>0.36098948170851941</v>
+        <v>0.3609894817085194</v>
       </c>
       <c r="H15">
-        <v>0.36074058874220433</v>
+        <v>0.3607405887422043</v>
       </c>
       <c r="I15">
-        <v>0.33130765958961089</v>
+        <v>0.3313076595896109</v>
       </c>
       <c r="J15">
-        <v>0.39128387212110233</v>
+        <v>0.3912838721211023</v>
       </c>
       <c r="K15">
-        <v>5.5686907435962612E-52</v>
+        <v>5.568690743596261E-52</v>
       </c>
       <c r="L15">
         <v>1.795754237474857E+51</v>
